--- a/data/trans_orig/P19C02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C02-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2007 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85041</t>
+          <t>86703</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123408</t>
+          <t>125077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102885</t>
+          <t>102379</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140324</t>
+          <t>141361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198991</t>
+          <t>198588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251955</t>
+          <t>254156</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354429</t>
+          <t>352760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392796</t>
+          <t>391134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>396763</t>
+          <t>395726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>434202</t>
+          <t>434708</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>762969</t>
+          <t>760768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815933</t>
+          <t>816336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,43%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>171784</t>
+          <t>168028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>221620</t>
+          <t>218407</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>203694</t>
+          <t>203146</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>255936</t>
+          <t>256454</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>384478</t>
+          <t>389057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>460759</t>
+          <t>459780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500508</t>
+          <t>503721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>550344</t>
+          <t>554100</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>548290</t>
+          <t>547772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>600532</t>
+          <t>601080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1065595</t>
+          <t>1066574</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1141876</t>
+          <t>1137297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>143204</t>
+          <t>144653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187722</t>
+          <t>189035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174442</t>
+          <t>174580</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>221750</t>
+          <t>221094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>330137</t>
+          <t>329581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392146</t>
+          <t>388384</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>357367</t>
+          <t>356054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>401885</t>
+          <t>400436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>361878</t>
+          <t>362534</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>409186</t>
+          <t>409048</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>736571</t>
+          <t>740333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>798580</t>
+          <t>799136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217227</t>
+          <t>217833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>265225</t>
+          <t>267326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>225594</t>
+          <t>224640</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>280081</t>
+          <t>278694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>455523</t>
+          <t>457402</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>527552</t>
+          <t>528308</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>444463</t>
+          <t>442362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>492461</t>
+          <t>491855</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>532986</t>
+          <t>534373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>587473</t>
+          <t>588427</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>995203</t>
+          <t>994447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1067232</t>
+          <t>1065353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>660275</t>
+          <t>658676</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>751819</t>
+          <t>746373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>754103</t>
+          <t>747514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>843476</t>
+          <t>844575</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1431757</t>
+          <t>1434830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1566168</t>
+          <t>1562899</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1702923</t>
+          <t>1708369</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1794467</t>
+          <t>1796066</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1894533</t>
+          <t>1893434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1983906</t>
+          <t>1990495</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3626582</t>
+          <t>3629851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3760993</t>
+          <t>3757920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113884</t>
+          <t>113957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155013</t>
+          <t>155201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>158225</t>
+          <t>161906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>208060</t>
+          <t>208423</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>286244</t>
+          <t>285580</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>347197</t>
+          <t>349954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449890</t>
+          <t>449702</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491019</t>
+          <t>490946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428680</t>
+          <t>428317</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>478515</t>
+          <t>474834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>894446</t>
+          <t>891689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>955399</t>
+          <t>956063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>234278</t>
+          <t>234350</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>289526</t>
+          <t>291132</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>211095</t>
+          <t>210506</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>264235</t>
+          <t>265414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>462187</t>
+          <t>458685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>541174</t>
+          <t>538021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>576460</t>
+          <t>574854</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>631708</t>
+          <t>631636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>635629</t>
+          <t>634450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>688769</t>
+          <t>689358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1224676</t>
+          <t>1227829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1303663</t>
+          <t>1307165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158345</t>
+          <t>159661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>205122</t>
+          <t>208667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>206129</t>
+          <t>201429</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>257030</t>
+          <t>255781</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>380069</t>
+          <t>379168</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>449163</t>
+          <t>450874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>430911</t>
+          <t>427366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>477688</t>
+          <t>476372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>421467</t>
+          <t>422716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>472368</t>
+          <t>477068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>865366</t>
+          <t>863655</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>934460</t>
+          <t>935361</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>259637</t>
+          <t>261187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>314590</t>
+          <t>315096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>301737</t>
+          <t>301090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>361453</t>
+          <t>364891</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>582379</t>
+          <t>580166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>661560</t>
+          <t>660427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,0%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>490094</t>
+          <t>489588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>545047</t>
+          <t>543497</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>571748</t>
+          <t>568310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>631464</t>
+          <t>632111</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1076325</t>
+          <t>1077458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1155506</t>
+          <t>1157719</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>810594</t>
+          <t>813097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>914182</t>
+          <t>915239</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>935900</t>
+          <t>924557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1040413</t>
+          <t>1035890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1782601</t>
+          <t>1772288</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1927511</t>
+          <t>1921758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1997424</t>
+          <t>1996367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2101012</t>
+          <t>2098509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2107889</t>
+          <t>2112412</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2212402</t>
+          <t>2223745</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4132397</t>
+          <t>4138150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4277307</t>
+          <t>4287620</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127981</t>
+          <t>127135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168853</t>
+          <t>167761</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>142819</t>
+          <t>144938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185849</t>
+          <t>186278</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287970</t>
+          <t>284745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>345156</t>
+          <t>341542</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356140</t>
+          <t>357232</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397012</t>
+          <t>397858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>358514</t>
+          <t>358085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401544</t>
+          <t>399425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>724200</t>
+          <t>727814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>781386</t>
+          <t>784611</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,37%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>273310</t>
+          <t>274413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>330218</t>
+          <t>329795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>301659</t>
+          <t>302347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>361964</t>
+          <t>361700</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>593993</t>
+          <t>589830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>676938</t>
+          <t>675404</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,14%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>486128</t>
+          <t>486551</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>543036</t>
+          <t>541933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504409</t>
+          <t>504673</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>564714</t>
+          <t>564026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005781</t>
+          <t>1007315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1088726</t>
+          <t>1092889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>161360</t>
+          <t>163310</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>205845</t>
+          <t>209138</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210937</t>
+          <t>207290</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>258454</t>
+          <t>257287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>384231</t>
+          <t>384178</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>447844</t>
+          <t>448170</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,66%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>344515</t>
+          <t>341222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>389000</t>
+          <t>387050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321284</t>
+          <t>322451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>368801</t>
+          <t>372448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>682254</t>
+          <t>681928</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>745867</t>
+          <t>745920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>267060</t>
+          <t>266271</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>319447</t>
+          <t>318628</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>307839</t>
+          <t>308235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364514</t>
+          <t>366694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>589895</t>
+          <t>591742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>670786</t>
+          <t>669958</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>453188</t>
+          <t>454007</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>505575</t>
+          <t>506364</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>512327</t>
+          <t>510147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>569002</t>
+          <t>568606</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>978690</t>
+          <t>979518</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1059581</t>
+          <t>1057734</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>879600</t>
+          <t>877134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>976764</t>
+          <t>974335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1009448</t>
+          <t>1011762</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1119982</t>
+          <t>1112294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1919510</t>
+          <t>1924967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2064428</t>
+          <t>2070108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1687569</t>
+          <t>1689998</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1784733</t>
+          <t>1787199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1747333</t>
+          <t>1755021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1857867</t>
+          <t>1855553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3467220</t>
+          <t>3461540</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3612138</t>
+          <t>3606681</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>228120</t>
+          <t>230002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>280321</t>
+          <t>284369</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>293568</t>
+          <t>292987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>333395</t>
+          <t>333323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>534817</t>
+          <t>536273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>601640</t>
+          <t>603013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>330983</t>
+          <t>326935</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>383184</t>
+          <t>381302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>318137</t>
+          <t>318209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357964</t>
+          <t>358545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>661196</t>
+          <t>659823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>728019</t>
+          <t>726563</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>256898</t>
+          <t>254170</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>606972</t>
+          <t>607658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>460228</t>
+          <t>458954</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>514201</t>
+          <t>513653</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>615020</t>
+          <t>587796</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1093423</t>
+          <t>1091913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>559482</t>
+          <t>558796</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>909556</t>
+          <t>912284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>428124</t>
+          <t>428672</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>482097</t>
+          <t>483371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1015356</t>
+          <t>1016866</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1493759</t>
+          <t>1520983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>269954</t>
+          <t>271707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>332465</t>
+          <t>333288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>354535</t>
+          <t>354928</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>701190</t>
+          <t>711831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>659330</t>
+          <t>659522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1139968</t>
+          <t>1089161</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>67,72%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>353802</t>
+          <t>352979</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>416313</t>
+          <t>414560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>220863</t>
+          <t>210222</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>567518</t>
+          <t>567125</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>468352</t>
+          <t>519159</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>948990</t>
+          <t>948798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>406118</t>
+          <t>405384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>470174</t>
+          <t>467932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>390116</t>
+          <t>391768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>539364</t>
+          <t>535178</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>808865</t>
+          <t>813876</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>981832</t>
+          <t>979448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>419761</t>
+          <t>422003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>483817</t>
+          <t>484551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>523553</t>
+          <t>527739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>672801</t>
+          <t>671149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>971019</t>
+          <t>973403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1143986</t>
+          <t>1138975</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,32%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1134610</t>
+          <t>1140942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1595896</t>
+          <t>1588859</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1646831</t>
+          <t>1639898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2130632</t>
+          <t>2089353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2905594</t>
+          <t>2925284</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3533389</t>
+          <t>3527322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1758064</t>
+          <t>1765101</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2219350</t>
+          <t>2213018</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1448195</t>
+          <t>1489474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1931996</t>
+          <t>1938929</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3399398</t>
+          <t>3405465</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4027193</t>
+          <t>4007503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C02-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86703</t>
+          <t>85149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125077</t>
+          <t>121132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,49 +748,49 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>25,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>103421</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>140633</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>26,18%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>120303</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>102379</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>141361</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>22,4%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>26,32%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>219</t>
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198588</t>
+          <t>200731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254156</t>
+          <t>251151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>352760</t>
+          <t>356705</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391134</t>
+          <t>392688</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,47 +861,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>74,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>82,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>416784</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>396454</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>433666</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>77,6%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>73,82%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>416784</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>395726</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>434708</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>77,6%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>73,68%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>760768</t>
+          <t>763773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>816336</t>
+          <t>814193</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168028</t>
+          <t>169005</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>218407</t>
+          <t>222540</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>203146</t>
+          <t>204473</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>256454</t>
+          <t>258228</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>389057</t>
+          <t>388617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>459780</t>
+          <t>459510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>503721</t>
+          <t>499588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>554100</t>
+          <t>553123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>547772</t>
+          <t>545998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>601080</t>
+          <t>599753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1066574</t>
+          <t>1066844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1137297</t>
+          <t>1137737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,54%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144653</t>
+          <t>141919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189035</t>
+          <t>186784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>174580</t>
+          <t>173193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>221094</t>
+          <t>218758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>329581</t>
+          <t>326042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>388384</t>
+          <t>390617</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>356054</t>
+          <t>358305</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>400436</t>
+          <t>403170</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>362534</t>
+          <t>364870</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>409048</t>
+          <t>410435</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>740333</t>
+          <t>738100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>799136</t>
+          <t>802675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217833</t>
+          <t>216628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>267326</t>
+          <t>266236</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224640</t>
+          <t>225993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>278694</t>
+          <t>280843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>457402</t>
+          <t>454970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>528308</t>
+          <t>527175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>442362</t>
+          <t>443452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>491855</t>
+          <t>493060</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>534373</t>
+          <t>532224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>588427</t>
+          <t>587074</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>994447</t>
+          <t>995580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1065353</t>
+          <t>1067785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>658676</t>
+          <t>659841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>746373</t>
+          <t>748681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>747514</t>
+          <t>752463</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>844575</t>
+          <t>845461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1434830</t>
+          <t>1433902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1562899</t>
+          <t>1560556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1708369</t>
+          <t>1706061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1796066</t>
+          <t>1794901</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1893434</t>
+          <t>1892548</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1990495</t>
+          <t>1985546</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3629851</t>
+          <t>3632194</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3757920</t>
+          <t>3758848</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113957</t>
+          <t>111491</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155201</t>
+          <t>153179</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>161906</t>
+          <t>158265</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>208423</t>
+          <t>206720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>285580</t>
+          <t>286109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>349954</t>
+          <t>347798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449702</t>
+          <t>451724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490946</t>
+          <t>493412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428317</t>
+          <t>430020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>474834</t>
+          <t>478475</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>891689</t>
+          <t>893845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>956063</t>
+          <t>955534</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,96%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>234350</t>
+          <t>236395</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>291132</t>
+          <t>291296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>210506</t>
+          <t>212481</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>265414</t>
+          <t>267322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>458685</t>
+          <t>465130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>538021</t>
+          <t>540585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>574854</t>
+          <t>574690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>631636</t>
+          <t>629591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>634450</t>
+          <t>632542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>689358</t>
+          <t>687383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1227829</t>
+          <t>1225265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1307165</t>
+          <t>1300720</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,66%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>159661</t>
+          <t>159400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>208667</t>
+          <t>207941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201429</t>
+          <t>206012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>255781</t>
+          <t>257626</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>379168</t>
+          <t>378326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>450874</t>
+          <t>451438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>427366</t>
+          <t>428092</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>476372</t>
+          <t>476633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>422716</t>
+          <t>420871</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>477068</t>
+          <t>472485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>863655</t>
+          <t>863091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935361</t>
+          <t>936203</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>261187</t>
+          <t>262828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>315096</t>
+          <t>316968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>301090</t>
+          <t>301903</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364891</t>
+          <t>362544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>580166</t>
+          <t>578437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>660427</t>
+          <t>659398</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>489588</t>
+          <t>487716</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>543497</t>
+          <t>541856</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>568310</t>
+          <t>570657</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>632111</t>
+          <t>631298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1077458</t>
+          <t>1078487</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1157719</t>
+          <t>1159448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>813097</t>
+          <t>810338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>915239</t>
+          <t>915626</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>924557</t>
+          <t>925666</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1035890</t>
+          <t>1036465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1772288</t>
+          <t>1778019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1921758</t>
+          <t>1922867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1996367</t>
+          <t>1995980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2098509</t>
+          <t>2101268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2112412</t>
+          <t>2111837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2223745</t>
+          <t>2222636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4138150</t>
+          <t>4137041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4287620</t>
+          <t>4281889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,66%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127135</t>
+          <t>128559</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>167761</t>
+          <t>170846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>144938</t>
+          <t>143085</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186278</t>
+          <t>186129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>284745</t>
+          <t>282640</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>341542</t>
+          <t>340853</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>357232</t>
+          <t>354147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397858</t>
+          <t>396434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>358085</t>
+          <t>358234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>399425</t>
+          <t>401278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727814</t>
+          <t>728503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>784611</t>
+          <t>786716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>274413</t>
+          <t>271420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>329795</t>
+          <t>331571</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>302347</t>
+          <t>303139</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>361700</t>
+          <t>362788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>589830</t>
+          <t>590356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>675404</t>
+          <t>674734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>486551</t>
+          <t>484775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>541933</t>
+          <t>544926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504673</t>
+          <t>503585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>564026</t>
+          <t>563234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1007315</t>
+          <t>1007985</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1092889</t>
+          <t>1092363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,92%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163310</t>
+          <t>157773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209138</t>
+          <t>205563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207290</t>
+          <t>208757</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>257287</t>
+          <t>257272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>384178</t>
+          <t>386305</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>448170</t>
+          <t>449577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>341222</t>
+          <t>344797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>387050</t>
+          <t>392587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322451</t>
+          <t>322466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>372448</t>
+          <t>370981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>681928</t>
+          <t>680521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>745920</t>
+          <t>743793</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>266271</t>
+          <t>266518</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>318628</t>
+          <t>321335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>308235</t>
+          <t>308724</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>366694</t>
+          <t>366071</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>591742</t>
+          <t>588373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>669958</t>
+          <t>672197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>454007</t>
+          <t>451300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>506364</t>
+          <t>506117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>510147</t>
+          <t>510770</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>568606</t>
+          <t>568117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>979518</t>
+          <t>977279</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1057734</t>
+          <t>1061103</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,33%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>877134</t>
+          <t>878313</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>974335</t>
+          <t>979996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1011762</t>
+          <t>1011202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1112294</t>
+          <t>1118218</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1924967</t>
+          <t>1924204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2070108</t>
+          <t>2069709</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1689998</t>
+          <t>1684337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1787199</t>
+          <t>1786020</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1755021</t>
+          <t>1749097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1855553</t>
+          <t>1856113</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3461540</t>
+          <t>3461939</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3606681</t>
+          <t>3607444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>255632</t>
+          <t>283399</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>230002</t>
+          <t>256638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>284369</t>
+          <t>312018</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>313992</t>
+          <t>345113</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>292987</t>
+          <t>321648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>333323</t>
+          <t>365952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>569624</t>
+          <t>628512</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>536273</t>
+          <t>594588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>603013</t>
+          <t>667715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,89%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>355672</t>
+          <t>376132</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326935</t>
+          <t>347513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>381302</t>
+          <t>402893</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>337540</t>
+          <t>361036</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>318209</t>
+          <t>340197</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>358545</t>
+          <t>384501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>693212</t>
+          <t>737168</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>659823</t>
+          <t>697965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>726563</t>
+          <t>771092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>56,46%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>467618</t>
+          <t>519411</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>254170</t>
+          <t>485893</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>607658</t>
+          <t>557900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>486532</t>
+          <t>545325</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>458954</t>
+          <t>513093</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>513653</t>
+          <t>570324</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>954150</t>
+          <t>1064736</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>587796</t>
+          <t>1019361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1091913</t>
+          <t>1107355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>698836</t>
+          <t>496798</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>558796</t>
+          <t>458309</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>912284</t>
+          <t>530316</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>455793</t>
+          <t>502459</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>428672</t>
+          <t>477460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>483371</t>
+          <t>534691</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1154629</t>
+          <t>999257</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1016866</t>
+          <t>956638</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1520983</t>
+          <t>1044632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>50,61%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1166454</t>
+          <t>1016209</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1166454</t>
+          <t>1016209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1166454</t>
+          <t>1016209</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2108779</t>
+          <t>2063993</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2108779</t>
+          <t>2063993</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2108779</t>
+          <t>2063993</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>301860</t>
+          <t>336340</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>271707</t>
+          <t>306220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>333288</t>
+          <t>371049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>491764</t>
+          <t>340230</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>354928</t>
+          <t>313851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>711831</t>
+          <t>365488</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>793624</t>
+          <t>676571</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>659522</t>
+          <t>636558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1089161</t>
+          <t>719965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>384407</t>
+          <t>437668</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>352979</t>
+          <t>402959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>414560</t>
+          <t>467788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>430289</t>
+          <t>455115</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210222</t>
+          <t>429857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>567125</t>
+          <t>481494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>814696</t>
+          <t>892782</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519159</t>
+          <t>849388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>948798</t>
+          <t>932795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,44%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>435504</t>
+          <t>463115</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>405384</t>
+          <t>429207</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>467932</t>
+          <t>496390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>489922</t>
+          <t>532895</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>391768</t>
+          <t>503358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>535178</t>
+          <t>561473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>925426</t>
+          <t>996011</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>813876</t>
+          <t>952494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>979448</t>
+          <t>1041084</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>454431</t>
+          <t>484844</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>422003</t>
+          <t>451569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>484551</t>
+          <t>518752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>572995</t>
+          <t>543275</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>527739</t>
+          <t>514697</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>671149</t>
+          <t>572812</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1027425</t>
+          <t>1028118</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>973403</t>
+          <t>983045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1138975</t>
+          <t>1071635</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1460614</t>
+          <t>1602266</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1140942</t>
+          <t>1534252</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1588859</t>
+          <t>1669016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1782210</t>
+          <t>1763564</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1639898</t>
+          <t>1713086</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2089353</t>
+          <t>1816654</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3242824</t>
+          <t>3365829</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2925284</t>
+          <t>3272423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3527322</t>
+          <t>3448444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1893346</t>
+          <t>1795441</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1765101</t>
+          <t>1728691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2213018</t>
+          <t>1863455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1796617</t>
+          <t>1861884</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1489474</t>
+          <t>1808794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1938929</t>
+          <t>1912362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3689963</t>
+          <t>3657326</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3405465</t>
+          <t>3574711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4007503</t>
+          <t>3750732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3353960</t>
+          <t>3397707</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3353960</t>
+          <t>3397707</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3353960</t>
+          <t>3397707</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6932787</t>
+          <t>7023155</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6932787</t>
+          <t>7023155</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6932787</t>
+          <t>7023155</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
